--- a/docs/oc-mensuales/emergencias-contingencias-y-prevencion/sep-2025.xlsx
+++ b/docs/oc-mensuales/emergencias-contingencias-y-prevencion/sep-2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC sep-2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC sep-2025" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,7 +549,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3355,7 +3355,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -4087,7 +4087,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4209,7 +4209,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4514,7 +4514,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4575,7 +4575,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4636,7 +4636,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4758,7 +4758,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4819,7 +4819,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -5002,7 +5002,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -5063,7 +5063,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -5307,7 +5307,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -5551,7 +5551,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -5673,7 +5673,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -5734,7 +5734,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -5795,7 +5795,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -5856,7 +5856,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -5917,7 +5917,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -6039,7 +6039,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -6100,7 +6100,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -6222,7 +6222,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -6344,7 +6344,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -6405,7 +6405,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -6527,7 +6527,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -6588,7 +6588,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -6649,7 +6649,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -6710,7 +6710,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -6832,7 +6832,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -6893,7 +6893,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -7015,7 +7015,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -7076,7 +7076,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -7137,7 +7137,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -7259,7 +7259,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -7320,7 +7320,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -7381,7 +7381,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -7442,7 +7442,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -7503,7 +7503,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -7564,7 +7564,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -7625,7 +7625,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -7686,7 +7686,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -7747,7 +7747,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -7808,7 +7808,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -7823,7 +7823,7 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -7873,7 +7873,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -7934,7 +7934,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -7995,7 +7995,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -8056,7 +8056,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -8117,7 +8117,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -8178,7 +8178,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -8300,7 +8300,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -8422,7 +8422,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -8483,7 +8483,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -8605,7 +8605,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -8666,7 +8666,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -8727,7 +8727,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -8788,7 +8788,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -8849,7 +8849,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -8910,7 +8910,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -8971,7 +8971,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -9032,7 +9032,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -9093,7 +9093,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -9154,7 +9154,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -9215,7 +9215,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -9337,7 +9337,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -9398,7 +9398,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -9459,7 +9459,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -9520,7 +9520,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -9642,7 +9642,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -9703,7 +9703,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -9764,7 +9764,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -9825,7 +9825,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -9886,7 +9886,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -9947,7 +9947,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -10008,7 +10008,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -10069,7 +10069,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -10130,7 +10130,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -10191,7 +10191,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -10252,7 +10252,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -10313,7 +10313,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -10374,7 +10374,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -10435,7 +10435,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -10496,7 +10496,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -10557,7 +10557,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -10618,7 +10618,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -10679,7 +10679,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -10740,7 +10740,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -10801,7 +10801,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -10862,7 +10862,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -10923,7 +10923,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -10984,7 +10984,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -11045,7 +11045,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -11106,7 +11106,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -11167,7 +11167,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -11228,7 +11228,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -11289,7 +11289,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -11350,7 +11350,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -11411,7 +11411,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -11472,7 +11472,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -11533,7 +11533,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -11594,7 +11594,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -11655,7 +11655,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -11716,7 +11716,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -11777,7 +11777,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -11838,7 +11838,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -11899,7 +11899,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -11960,7 +11960,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -12021,7 +12021,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -12082,7 +12082,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -12143,7 +12143,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -12204,7 +12204,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -12265,7 +12265,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -12326,7 +12326,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -12387,7 +12387,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -12448,7 +12448,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -12509,7 +12509,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -12570,7 +12570,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -12631,7 +12631,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -12692,7 +12692,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -12753,7 +12753,7 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -12814,7 +12814,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -12875,7 +12875,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -12936,7 +12936,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -12997,7 +12997,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -13058,7 +13058,7 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -13119,7 +13119,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -13180,7 +13180,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -13241,7 +13241,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -13302,7 +13302,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -13363,7 +13363,7 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -13424,7 +13424,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -13485,7 +13485,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -13546,7 +13546,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">

--- a/docs/oc-mensuales/emergencias-contingencias-y-prevencion/sep-2025.xlsx
+++ b/docs/oc-mensuales/emergencias-contingencias-y-prevencion/sep-2025.xlsx
@@ -745,7 +745,11 @@
           <t>77.765.995-2</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +932,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1180,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1245,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1432,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1497,11 @@
           <t>77.765.995-2</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1623,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1810,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2180,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2489,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2554,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2636,7 +2680,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2745,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2880,7 +2932,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3002,7 +3058,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3063,7 +3123,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3124,7 +3188,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3185,7 +3253,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3307,7 +3379,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3429,7 +3505,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3490,7 +3570,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3612,7 +3696,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3673,7 +3761,11 @@
           <t>77.765.995-2</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3734,7 +3826,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4161,7 +4257,11 @@
           <t>77.909.208-9</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4222,7 +4322,11 @@
           <t>77.909.208-9</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4405,7 +4509,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4466,7 +4574,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4527,7 +4639,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4588,7 +4704,11 @@
           <t>77.765.995-2</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4771,7 +4891,11 @@
           <t>77.765.995-2</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4832,7 +4956,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4893,7 +5021,11 @@
           <t>77.765.995-2</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4954,7 +5086,11 @@
           <t>77.544.929-2</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5259,7 +5395,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5564,7 +5704,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5747,7 +5891,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6052,7 +6200,11 @@
           <t>77.801.815-2</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6357,7 +6509,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6418,7 +6574,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6479,7 +6639,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6784,7 +6948,11 @@
           <t>77.765.995-2</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6845,7 +7013,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7394,7 +7566,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7699,7 +7875,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7947,7 +8127,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L123" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8069,7 +8253,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8130,7 +8318,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L126" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8191,7 +8383,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8252,7 +8448,11 @@
           <t>77.814.662-2</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8435,7 +8635,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8740,7 +8944,11 @@
           <t>77.765.995-2</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L136" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8862,7 +9070,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8984,7 +9196,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9045,7 +9261,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9106,7 +9326,11 @@
           <t>77.765.995-2</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L142" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9167,7 +9391,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9228,7 +9456,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L144" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9289,7 +9521,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9411,7 +9647,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L147" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9533,7 +9773,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr"/>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L149" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9594,7 +9838,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9655,7 +9903,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9716,7 +9968,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9899,7 +10155,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9960,7 +10220,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10082,7 +10346,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10143,7 +10411,11 @@
           <t>77.721.492-6</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L159" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10326,7 +10598,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10387,7 +10663,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L163" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10570,7 +10850,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L166" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10631,7 +10915,11 @@
           <t>77.765.995-2</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10753,7 +11041,11 @@
           <t>77.765.995-2</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10814,7 +11106,11 @@
           <t>77.765.995-2</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L170" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10875,7 +11171,11 @@
           <t>77.765.995-2</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L171" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10997,7 +11297,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L173" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11180,7 +11484,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L176" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11241,7 +11549,11 @@
           <t>78.094.280-0</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L177" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11302,7 +11614,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L178" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11363,7 +11679,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L179" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11485,7 +11805,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L181" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11607,7 +11931,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L183" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11729,7 +12057,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L185" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11912,7 +12244,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L188" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11973,7 +12309,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L189" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12034,7 +12374,11 @@
           <t>77.765.995-2</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L190" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12095,7 +12439,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L191" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12278,7 +12626,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr"/>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L194" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12522,7 +12874,11 @@
           <t>77.765.995-2</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L198" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12644,7 +13000,11 @@
           <t>77.801.815-2</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L200" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12827,7 +13187,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr"/>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L203" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12888,7 +13252,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr"/>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L204" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13010,7 +13378,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr"/>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L206" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13193,7 +13565,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr"/>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L209" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13498,7 +13874,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr"/>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L214" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13559,7 +13939,11 @@
           <t>77.721.492-6</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L215" t="inlineStr">
         <is>
           <t>USD</t>
